--- a/tests/reference_data/test_scenario_fms_unconstrained.xlsx
+++ b/tests/reference_data/test_scenario_fms_unconstrained.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D016AA9-DF0C-4AF3-BD47-B40FDA0993E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8002E2-E6B5-4D5F-8F5B-9B83B5E243F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="2850" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-25635" yWindow="2265" windowWidth="21600" windowHeight="11295" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="240">
   <si>
     <t>Years</t>
   </si>
@@ -810,6 +810,9 @@
   </si>
   <si>
     <t>prioritize_transformation_stages</t>
+  </si>
+  <si>
+    <t>Comment (expected result)</t>
   </si>
 </sst>
 </file>
@@ -1818,6 +1821,9 @@
       <c r="B27" t="s">
         <v>160</v>
       </c>
+      <c r="C27" t="s">
+        <v>181</v>
+      </c>
       <c r="D27" t="s">
         <v>125</v>
       </c>
@@ -5017,91 +5023,95 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43406F76-D4E1-4DE8-A811-C2AB881D41ED}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="52.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="E1" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="F1" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="G1" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="H1" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="I1" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="J1" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="K1" s="25" t="s">
         <v>208</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>114</v>
       </c>
       <c r="L1" s="25" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="M1" s="25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D2">
-        <v>-50</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>2025</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>2030</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="24" t="b">
+      <c r="K2" s="24" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -5110,7 +5120,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{008CAED9-3C22-4095-9218-2455CD3CED8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2" xr:uid="{008CAED9-3C22-4095-9218-2455CD3CED8E}">
       <formula1>Boolean</formula1>
     </dataValidation>
   </dataValidations>
@@ -5122,13 +5132,13 @@
           <x14:formula1>
             <xm:f>'Data validation parameters'!$F$6:$F$9</xm:f>
           </x14:formula1>
-          <xm:sqref>J3:J1048576 I2:I1048576</xm:sqref>
+          <xm:sqref>K3:K1048576 J2:J1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{21908276-F864-4CA4-BA65-3DBA76B06B97}">
           <x14:formula1>
             <xm:f>'Data validation parameters'!$E$6:$E$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F1048576</xm:sqref>
+          <xm:sqref>G2:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5372,15 +5382,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
@@ -5390,6 +5391,15 @@
     <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5656,14 +5666,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5676,6 +5678,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
